--- a/artfynd/A 2153-2026 artfynd.xlsx
+++ b/artfynd/A 2153-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129627625</v>
+        <v>129627633</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -777,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129627633</v>
+        <v>129627625</v>
       </c>
       <c r="B3" t="n">
-        <v>92258</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +795,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
